--- a/90minutersdata/Player/2026/malvakter.xlsx
+++ b/90minutersdata/Player/2026/malvakter.xlsx
@@ -484,307 +484,307 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J. RinneJ. Rinne</t>
+          <t>K. NordfeldtK. Nordfeldt</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>296</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>786</v>
       </c>
       <c r="J2" t="n">
-        <v>210</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H. GustafssonH. Gustafsson</t>
+          <t>W. HahnW. Hahn</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>197</v>
+        <v>283</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>909</v>
+        <v>786</v>
       </c>
       <c r="J3" t="n">
-        <v>172</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>W. HahnW. Hahn</t>
+          <t>J. RinneJ. Rinne</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>95</v>
+        <v>307</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>769</v>
       </c>
       <c r="J4" t="n">
-        <v>110</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>K. NordfeldtK. Nordfeldt</t>
+          <t>R. OlsenR. Olsen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>309</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="n">
-        <v>97</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
-        <v>833</v>
+        <v>846</v>
       </c>
       <c r="J5" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>E. JägerE. Jäger</t>
+          <t>A. LindeA. Linde</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. LindeA. Linde</t>
+          <t>J. KindbergJ. Kindberg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
+        <v>302</v>
+      </c>
+      <c r="F7" t="n">
+        <v>17</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>706</v>
+      </c>
+      <c r="J7" t="n">
         <v>48</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R. OlsenR. Olsen</t>
+          <t>E. JÃ¤gerE. JÃ¤ger</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>301</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="n">
-        <v>98</v>
-      </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" t="n">
-        <v>833</v>
+        <v>538</v>
       </c>
       <c r="J8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>K. SimsK. Sims</t>
+          <t>A. DidrikssonA. Didriksson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D. ČelićD. Čelić</t>
+          <t>A. DzevlanA. Dzevlan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>E. BishesariE. Bishesari</t>
+          <t>A. FagerstrÃ¶mA. FagerstrÃ¶m</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>636</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A. DidrikssonA. Didriksson</t>
+          <t>A. LundinA. Lundin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -814,7 +814,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A. DzevlanA. Dzevlan</t>
+          <t>A. RahmA. Rahm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -844,7 +844,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A. FagerströmA. Fagerström</t>
+          <t>AndrÃ© BernardiniAndrÃ© Bernardini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -874,7 +874,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A. Kiilerich HermansenA. Kiilerich Hermansen</t>
+          <t>C. AnderssonC. Andersson</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -904,7 +904,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A. LundinA. Lundin</t>
+          <t>C. IsakssonC. Isaksson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -934,7 +934,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A. RahmA. Rahm</t>
+          <t>D. BlaÅ¾eviÄD. BlaÅ¾eviÄ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -964,7 +964,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>André BernardiniAndré Bernardini</t>
+          <t>E. BerishaE. Berisha</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -994,7 +994,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C. AnderssonC. Andersson</t>
+          <t>F. AnderssonF. Andersson</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C. IsakssonC. Isaksson</t>
+          <t>F. JakobssonF. Jakobsson</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D. BlaževićD. Blažević</t>
+          <t>F. ManojloviÄF. ManojloviÄ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1084,7 +1084,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>E. BerishaE. Berisha</t>
+          <t>H. FagerbergH. Fagerberg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>F. AnderssonF. Andersson</t>
+          <t>I. DiawaraI. Diawara</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>F. JakobssonF. Jakobsson</t>
+          <t>J. DahlinJ. Dahlin</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>F. ManojlovićF. Manojlović</t>
+          <t>J. RasheedJ. Rasheed</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H. FagerbergH. Fagerberg</t>
+          <t>K. JoelssonK. Joelsson</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1234,7 +1234,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>I. DiawaraI. Diawara</t>
+          <t>K. MarinkovicK. Marinkovic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1264,7 +1264,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>J. DahlinJ. Dahlin</t>
+          <t>L. HÃ¤gg-JohanssonL. HÃ¤gg-Johansson</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>J. RasheedJ. Rasheed</t>
+          <t>M. KrasniqiM. Krasniqi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1324,7 +1324,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>K. JoelssonK. Joelsson</t>
+          <t>M. NilssonM. Nilsson</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>K. MarinkovicK. Marinkovic</t>
+          <t>M. Nilsson SÃ¤fqvistM. Nilsson SÃ¤fqvist</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>L. Hägg-JohanssonL. Hägg-Johansson</t>
+          <t>R. ForsellR. Forsell</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1414,7 +1414,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M. KrasniqiM. Krasniqi</t>
+          <t>Ricardo FriedrichRicardo Friedrich</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1444,7 +1444,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>M. NilssonM. Nilsson</t>
+          <t>S. BrolinS. Brolin</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>M. Nilsson SäfqvistM. Nilsson Säfqvist</t>
+          <t>T. ErlandssonT. Erlandsson</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R. ForsellR. Forsell</t>
+          <t>V. AnderssonV. Andersson</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ricardo FriedrichRicardo Friedrich</t>
+          <t>W. JakobssonW. Jakobsson</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1564,7 +1564,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>S. BrolinS. Brolin</t>
+          <t>W. LundgrenW. Lundgren</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1594,7 +1594,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>T. ErlandssonT. Erlandsson</t>
+          <t>W. LykkeW. Lykke</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1624,127 +1624,127 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>V. AnderssonV. Andersson</t>
+          <t>R. WallinderR. Wallinder</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>667</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>W. JakobssonW. Jakobsson</t>
+          <t>D. ÄeliÄD. ÄeliÄ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>W. LundgrenW. Lundgren</t>
+          <t>M. IgonenM. Igonen</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-43</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>W. LykkeW. Lykke</t>
+          <t>I. PetterssonI. Pettersson</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>714</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>T. RönningT. Rönning</t>
+          <t>A. Kiilerich HermansenA. Kiilerich Hermansen</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G44" t="n">
         <v>2</v>
@@ -1764,190 +1764,190 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>667</v>
+        <v>600</v>
       </c>
       <c r="J44" t="n">
-        <v>-46</v>
+        <v>-47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>J. KindbergJ. Kindberg</t>
+          <t>K. SimsK. Sims</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>102</v>
+        <v>193</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="J45" t="n">
-        <v>-46</v>
+        <v>-66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>M. IgonenM. Igonen</t>
+          <t>E. BishesariE. Bishesari</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>100</v>
+        <v>294</v>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>250</v>
+        <v>643</v>
       </c>
       <c r="J46" t="n">
-        <v>-60</v>
+        <v>-71</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>D. AnderssonD. Andersson</t>
+          <t>H. GustafssonH. Gustafsson</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>153</v>
+        <v>289</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>750</v>
+        <v>667</v>
       </c>
       <c r="J47" t="n">
-        <v>-72</v>
+        <v>-74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>I. PetterssonI. Pettersson</t>
+          <t>D. AnderssonD. Andersson</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>197</v>
+        <v>254</v>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="J48" t="n">
-        <v>-97</v>
+        <v>-87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>L. CavalliusL. Cavallius</t>
+          <t>T. RÃ¶nningT. RÃ¶nning</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="J49" t="n">
-        <v>-101</v>
+        <v>-137</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>R. WallinderR. Wallinder</t>
+          <t>L. CavalliusL. Cavallius</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>194</v>
+        <v>294</v>
       </c>
       <c r="F50" t="n">
         <v>10</v>
       </c>
       <c r="G50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="J50" t="n">
-        <v>-144</v>
+        <v>-317</v>
       </c>
     </row>
   </sheetData>
